--- a/backend/templates/GSIS2.xlsx
+++ b/backend/templates/GSIS2.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\personal\folderFIS\Financial-Information-System\backend\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A12479-3643-43C5-8C42-007435351898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -232,66 +241,69 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="27">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
-      <sz val="16.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
@@ -299,7 +311,7 @@
       <b/>
       <i/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
@@ -307,19 +319,19 @@
       <b/>
       <i/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <i/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
@@ -327,7 +339,7 @@
       <b/>
       <i/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
@@ -335,67 +347,67 @@
       <b/>
       <i/>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <i/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
     <font>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <u/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <i/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <i/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Cambria"/>
     </font>
@@ -405,94 +417,136 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="47">
-    <border/>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -502,19 +556,27 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -529,93 +591,129 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -625,8 +723,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -636,48 +736,65 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -687,6 +804,7 @@
       <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -695,9 +813,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -712,38 +832,47 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -753,8 +882,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -764,6 +895,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -778,35 +910,45 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -816,613 +958,648 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="206">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="20" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="30" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="14" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="13" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="17" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="18" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="40" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="39" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="41" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="9" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf quotePrefix="1" borderId="18" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="9" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="42" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="43" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="44" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="45" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="46" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1431,9 +1608,15 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7029450" cy="1314450"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Shape 3"/>
+        <xdr:cNvPr id="3" name="Shape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1450,12 +1633,12 @@
         </a:ln>
       </xdr:spPr>
       <xdr:txBody>
-        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1470,7 +1653,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr b="1" lang="en-US" sz="900">
+            <a:rPr lang="en-US" sz="900" b="1">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1494,7 +1677,7 @@
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr b="1" lang="en-US" sz="900">
+            <a:rPr lang="en-US" sz="900" b="1">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1516,7 +1699,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1553,7 +1736,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1590,7 +1773,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1627,7 +1810,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1664,7 +1847,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1675,10 +1858,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:solidFill>
               <a:srgbClr val="3A7D22"/>
             </a:solidFill>
@@ -1689,7 +1869,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:lnSpc>
               <a:spcPct val="100000"/>
             </a:lnSpc>
@@ -1707,7 +1887,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr i="1" lang="en-US" sz="900">
+            <a:rPr lang="en-US" sz="900" i="1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1718,7 +1898,7 @@
             </a:rPr>
             <a:t>NIA-RO-AFD-FIN-INT-Form-209-Rev00</a:t>
           </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
@@ -1729,7 +1909,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1740,10 +1920,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:latin typeface="Arial"/>
             <a:ea typeface="Arial"/>
             <a:cs typeface="Arial"/>
@@ -1751,7 +1928,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1762,10 +1939,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:latin typeface="Arial"/>
             <a:ea typeface="Arial"/>
             <a:cs typeface="Arial"/>
@@ -1773,7 +1947,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1784,10 +1958,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:latin typeface="Arial"/>
             <a:ea typeface="Arial"/>
             <a:cs typeface="Arial"/>
@@ -1795,7 +1966,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1806,10 +1977,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:latin typeface="Arial"/>
             <a:ea typeface="Arial"/>
             <a:cs typeface="Arial"/>
@@ -1817,7 +1985,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1828,10 +1996,7 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr i="1" sz="900">
+          <a:endParaRPr sz="900" i="1">
             <a:latin typeface="Arial"/>
             <a:ea typeface="Arial"/>
             <a:cs typeface="Arial"/>
@@ -1839,7 +2004,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1850,9 +2015,6 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
           <a:endParaRPr sz="800">
             <a:latin typeface="Helvetica Neue"/>
             <a:ea typeface="Helvetica Neue"/>
@@ -1861,7 +2023,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1872,9 +2034,6 @@
             <a:buFont typeface="Arial"/>
             <a:buNone/>
           </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
           <a:endParaRPr sz="800">
             <a:latin typeface="Helvetica Neue"/>
             <a:ea typeface="Helvetica Neue"/>
@@ -1896,12 +2055,18 @@
     <xdr:ext cx="8982075" cy="1019175"/>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="Shape 2"/>
+        <xdr:cNvPr id="2" name="Shape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="854963" y="3270413"/>
+          <a:off x="123825" y="38100"/>
           <a:ext cx="8982075" cy="1019175"/>
           <a:chOff x="854963" y="3270413"/>
           <a:chExt cx="8982075" cy="1019175"/>
@@ -1909,7 +2074,13 @@
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="4" name="Shape 4"/>
+          <xdr:cNvPr id="4" name="Shape 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvGrpSpPr/>
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
@@ -1920,9 +2091,15 @@
             <a:chExt cx="8982075" cy="1019175"/>
           </a:xfrm>
         </xdr:grpSpPr>
-        <xdr:sp>
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="Shape 5"/>
+            <xdr:cNvPr id="5" name="Shape 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
           <xdr:spPr>
@@ -1939,12 +2116,12 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+            <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
               <a:noAutofit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
                 <a:spcBef>
                   <a:spcPts val="0"/>
                 </a:spcBef>
@@ -1953,16 +2130,19 @@
                 </a:spcAft>
                 <a:buNone/>
               </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
               <a:endParaRPr sz="1400"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="6" name="Shape 6"/>
+            <xdr:cNvPr id="6" name="Shape 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGrpSpPr/>
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
@@ -1973,9 +2153,15 @@
               <a:chExt cx="7679488" cy="1262061"/>
             </a:xfrm>
           </xdr:grpSpPr>
-          <xdr:sp>
+          <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="7" name="Shape 7"/>
+              <xdr:cNvPr id="7" name="Shape 7">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvSpPr/>
             </xdr:nvSpPr>
             <xdr:spPr>
@@ -1992,12 +2178,12 @@
               </a:ln>
             </xdr:spPr>
             <xdr:txBody>
-              <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+              <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="91425" rIns="91425" bIns="91425" anchor="ctr" anchorCtr="0">
                 <a:noAutofit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+                <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2008,16 +2194,19 @@
                   <a:buFont typeface="Arial"/>
                   <a:buNone/>
                 </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
                 <a:endParaRPr sz="1400"/>
               </a:p>
             </xdr:txBody>
           </xdr:sp>
           <xdr:grpSp>
             <xdr:nvGrpSpPr>
-              <xdr:cNvPr id="8" name="Shape 8"/>
+              <xdr:cNvPr id="8" name="Shape 8">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvGrpSpPr/>
             </xdr:nvGrpSpPr>
             <xdr:grpSpPr>
@@ -2030,14 +2219,20 @@
             </xdr:grpSpPr>
             <xdr:pic>
               <xdr:nvPicPr>
-                <xdr:cNvPr id="9" name="Shape 9"/>
+                <xdr:cNvPr id="9" name="Shape 9">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
                 <xdr:cNvPicPr preferRelativeResize="0"/>
               </xdr:nvPicPr>
               <xdr:blipFill rotWithShape="1">
-                <a:blip r:embed="rId1">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
                   <a:alphaModFix/>
                 </a:blip>
-                <a:srcRect b="0" l="0" r="0" t="0"/>
+                <a:srcRect/>
                 <a:stretch/>
               </xdr:blipFill>
               <xdr:spPr>
@@ -2056,14 +2251,20 @@
             </xdr:pic>
             <xdr:pic>
               <xdr:nvPicPr>
-                <xdr:cNvPr id="10" name="Shape 10"/>
+                <xdr:cNvPr id="10" name="Shape 10">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
                 <xdr:cNvPicPr preferRelativeResize="0"/>
               </xdr:nvPicPr>
               <xdr:blipFill rotWithShape="1">
-                <a:blip r:embed="rId2">
+                <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
                   <a:alphaModFix/>
                 </a:blip>
-                <a:srcRect b="0" l="0" r="0" t="0"/>
+                <a:srcRect/>
                 <a:stretch/>
               </xdr:blipFill>
               <xdr:spPr>
@@ -2083,14 +2284,20 @@
           </xdr:grpSp>
           <xdr:pic>
             <xdr:nvPicPr>
-              <xdr:cNvPr id="11" name="Shape 11"/>
+              <xdr:cNvPr id="11" name="Shape 11">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvPicPr preferRelativeResize="0"/>
             </xdr:nvPicPr>
             <xdr:blipFill rotWithShape="1">
-              <a:blip r:embed="rId3">
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
                 <a:alphaModFix/>
               </a:blip>
-              <a:srcRect b="0" l="0" r="0" t="0"/>
+              <a:srcRect/>
               <a:stretch/>
             </xdr:blipFill>
             <xdr:spPr>
@@ -2107,9 +2314,15 @@
               </a:ln>
             </xdr:spPr>
           </xdr:pic>
-          <xdr:sp>
+          <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="12" name="Shape 12"/>
+              <xdr:cNvPr id="12" name="Shape 12">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvSpPr txBox="1"/>
             </xdr:nvSpPr>
             <xdr:spPr>
@@ -2126,12 +2339,12 @@
               </a:ln>
             </xdr:spPr>
             <xdr:txBody>
-              <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+              <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="t" anchorCtr="0">
                 <a:noAutofit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2142,10 +2355,7 @@
                   <a:buFont typeface="Arial"/>
                   <a:buNone/>
                 </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr b="1" sz="1100">
+                <a:endParaRPr sz="1100" b="1">
                   <a:latin typeface="Cambria"/>
                   <a:ea typeface="Cambria"/>
                   <a:cs typeface="Cambria"/>
@@ -2153,7 +2363,7 @@
                 </a:endParaRPr>
               </a:p>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2165,7 +2375,7 @@
                   <a:buNone/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" lang="en-US" sz="1400">
+                  <a:rPr lang="en-US" sz="1400" b="1">
                     <a:latin typeface="Cambria"/>
                     <a:ea typeface="Cambria"/>
                     <a:cs typeface="Cambria"/>
@@ -2176,7 +2386,7 @@
                 <a:endParaRPr sz="1400"/>
               </a:p>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2188,7 +2398,7 @@
                   <a:buNone/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="0" lang="en-US" sz="1400">
+                  <a:rPr lang="en-US" sz="1400" b="0">
                     <a:latin typeface="Cambria"/>
                     <a:ea typeface="Cambria"/>
                     <a:cs typeface="Cambria"/>
@@ -2196,7 +2406,7 @@
                   </a:rPr>
                   <a:t>OFFICE OF THE PRESIDENT</a:t>
                 </a:r>
-                <a:endParaRPr b="0" sz="1400">
+                <a:endParaRPr sz="1400" b="0">
                   <a:latin typeface="Cambria"/>
                   <a:ea typeface="Cambria"/>
                   <a:cs typeface="Cambria"/>
@@ -2204,7 +2414,7 @@
                 </a:endParaRPr>
               </a:p>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2216,7 +2426,7 @@
                   <a:buNone/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" lang="en-US" sz="1600">
+                  <a:rPr lang="en-US" sz="1600" b="1">
                     <a:latin typeface="Arial"/>
                     <a:ea typeface="Arial"/>
                     <a:cs typeface="Arial"/>
@@ -2232,7 +2442,7 @@
                 </a:endParaRPr>
               </a:p>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:spcBef>
                     <a:spcPts val="0"/>
                   </a:spcBef>
@@ -2260,7 +2470,7 @@
                 </a:endParaRPr>
               </a:p>
               <a:p>
-                <a:pPr indent="0" lvl="0" marL="0" marR="0" rtl="0" algn="l">
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" rtl="0">
                   <a:lnSpc>
                     <a:spcPct val="107000"/>
                   </a:lnSpc>
@@ -2302,11 +2512,17 @@
     <xdr:ext cx="12325350" cy="2390775"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png"/>
+        <xdr:cNvPr id="13" name="image2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2330,11 +2546,17 @@
     <xdr:ext cx="1362075" cy="704850"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPr id="14" name="image1.jpg">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2352,7 +2574,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2542,1711 +2764,1855 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Q1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="16" width="9.14"/>
-    <col customWidth="1" min="17" max="17" width="39.29"/>
-    <col customWidth="1" min="18" max="26" width="9.14"/>
+    <col min="1" max="16" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="39.28515625" customWidth="1"/>
+    <col min="18" max="26" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="4" t="s">
+    <row r="1" spans="1:17" ht="15.75">
+      <c r="A1" s="178"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="142"/>
+      <c r="P1" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="3"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="5" t="s">
+      <c r="Q1" s="142"/>
+    </row>
+    <row r="2" spans="1:17" ht="20.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="180"/>
+      <c r="Q2" s="153"/>
+    </row>
+    <row r="3" spans="1:17" ht="15.75">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="121"/>
+      <c r="P3" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="13"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="17" t="s">
+      <c r="Q3" s="121"/>
+    </row>
+    <row r="4" spans="1:17" ht="18">
+      <c r="A4" s="4"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="184"/>
+      <c r="Q4" s="153"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="116"/>
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="189" t="s">
         <v>2</v>
       </c>
-      <c r="Q5" s="18"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="13"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="s">
+      <c r="Q5" s="158"/>
+    </row>
+    <row r="6" spans="1:17" ht="18">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="190"/>
+      <c r="Q6" s="121"/>
+    </row>
+    <row r="7" spans="1:17" ht="15.75">
+      <c r="A7" s="191" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="24"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="s">
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
+      <c r="N7" s="192"/>
+      <c r="O7" s="192"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.75">
+      <c r="A8" s="185" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="30" t="s">
+      <c r="B8" s="141"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="141"/>
+      <c r="O8" s="141"/>
+      <c r="P8" s="141"/>
+      <c r="Q8" s="142"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.75">
+      <c r="A9" s="143"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="30" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="30" t="s">
+      <c r="I9" s="13"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="31" t="s">
+      <c r="M9" s="13"/>
+      <c r="N9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="O9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="32"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="33"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="38"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="s">
+      <c r="P9" s="13"/>
+      <c r="Q9" s="15"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.75">
+      <c r="A10" s="144"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="187"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" spans="1:17" ht="20.25">
+      <c r="A11" s="185" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="39" t="s">
+      <c r="B11" s="141"/>
+      <c r="C11" s="188"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="40" t="s">
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="141"/>
+      <c r="P11" s="194" t="s">
         <v>12</v>
       </c>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="43"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="13"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="s">
+      <c r="Q11" s="142"/>
+    </row>
+    <row r="12" spans="1:17" ht="20.25">
+      <c r="A12" s="143"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="147"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="195"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="116"/>
+      <c r="O12" s="116"/>
+      <c r="P12" s="196"/>
+      <c r="Q12" s="121"/>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="18"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="49"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="50" t="s">
+      <c r="B13" s="132"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="158"/>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="144"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="166"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="119"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="139"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75">
+      <c r="A15" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="52" t="s">
+      <c r="B15" s="176"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
+      <c r="F15" s="176"/>
+      <c r="G15" s="176"/>
+      <c r="H15" s="176"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="176"/>
+      <c r="K15" s="198"/>
+      <c r="L15" s="177"/>
+      <c r="M15" s="198" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="51"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="52" t="s">
+      <c r="N15" s="176"/>
+      <c r="O15" s="177"/>
+      <c r="P15" s="198" t="s">
         <v>16</v>
       </c>
-      <c r="Q15" s="54"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="55"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="61"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63" t="s">
+      <c r="Q15" s="199"/>
+    </row>
+    <row r="16" spans="1:17" ht="15.75">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="26"/>
+    </row>
+    <row r="17" spans="1:17" ht="18">
+      <c r="A17" s="27"/>
+      <c r="B17" s="201" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="64"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="66" t="s">
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="129"/>
+      <c r="K17" s="202"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="P17" s="67"/>
-      <c r="Q17" s="68" t="str">
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30">
         <f>G27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="62"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="70"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="72"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="62"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="72"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="62"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="72"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="62"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="72"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="76"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="78"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="79"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="72"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="82" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="18">
+      <c r="A18" s="27"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="116"/>
+      <c r="H18" s="116"/>
+      <c r="I18" s="116"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="34"/>
+    </row>
+    <row r="19" spans="1:17" ht="18">
+      <c r="A19" s="27"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+      <c r="F19" s="116"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="116"/>
+      <c r="I19" s="116"/>
+      <c r="J19" s="129"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="34"/>
+    </row>
+    <row r="20" spans="1:17" ht="18">
+      <c r="A20" s="27"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="116"/>
+      <c r="H20" s="116"/>
+      <c r="I20" s="116"/>
+      <c r="J20" s="129"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="34"/>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A21" s="27"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="34"/>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="203"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="204"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="34"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="83" t="s">
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="84" t="str">
-        <f t="shared" ref="G23:G26" si="1">#REF!</f>
+      <c r="G23" s="44" t="e">
+        <f t="shared" ref="G23:G26" si="0">#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H23" s="84"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="72"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="76"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="82" t="s">
+      <c r="H23" s="44"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="34"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="83" t="s">
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="G24" s="44" t="e">
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="H24" s="84"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="72"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="76"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="82" t="s">
+      <c r="H24" s="44"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="34"/>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="83" t="s">
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="G25" s="44" t="e">
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="H25" s="84"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="81"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="72"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="76"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="85" t="s">
+      <c r="H25" s="44"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="34"/>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="83" t="s">
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="84" t="str">
-        <f t="shared" si="1"/>
+      <c r="G26" s="44" t="e">
+        <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="H26" s="86"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="81"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="72"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="76"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="80"/>
-      <c r="G27" s="89"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="72"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="76"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="81"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="92"/>
-      <c r="Q28" s="72"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="76"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="93" t="s">
+      <c r="H26" s="45"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="34"/>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="34"/>
+    </row>
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A28" s="38"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="34"/>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A29" s="38"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="94"/>
-      <c r="E29" s="86"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="81"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="69"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="92"/>
-      <c r="Q29" s="72"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="76"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="94" t="str">
+      <c r="D29" s="53"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="34"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A30" s="38"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="53" t="e">
         <f>G23</f>
         <v>#REF!</v>
       </c>
-      <c r="D30" s="94"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="96" t="s">
+      <c r="D30" s="53"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="91" t="str">
+      <c r="G30" s="50" t="e">
         <f>C30*0.05</f>
         <v>#REF!</v>
       </c>
-      <c r="H30" s="95"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="69"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="92"/>
-      <c r="Q30" s="72" t="str">
+      <c r="H30" s="54"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="34" t="e">
         <f>G30</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
-      <c r="H31" s="95"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="81"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="72"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="76"/>
-      <c r="B32" s="88"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="95"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="92"/>
-      <c r="Q32" s="72"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76"/>
-      <c r="B33" s="88"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="95"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="81"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="69"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="92"/>
-      <c r="Q33" s="72"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="76"/>
-      <c r="B34" s="98" t="s">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A31" s="38"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="34"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A32" s="38"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="34"/>
+    </row>
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A33" s="38"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="34"/>
+    </row>
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A34" s="38"/>
+      <c r="B34" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="77"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="95"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="69"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="92"/>
-      <c r="Q34" s="72"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="76"/>
-      <c r="B35" s="88"/>
-      <c r="C35" s="99" t="s">
+      <c r="C34" s="39"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="34"/>
+    </row>
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A35" s="38"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="93" t="s">
+      <c r="D35" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="97"/>
-      <c r="F35" s="95"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="81"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="92"/>
-      <c r="Q35" s="72"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="76"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="99" t="s">
+      <c r="E35" s="56"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="34"/>
+    </row>
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A36" s="38"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="93" t="s">
+      <c r="D36" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="97"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="91"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="92"/>
-      <c r="Q36" s="72"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="76"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="99" t="s">
+      <c r="E36" s="56"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="34"/>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="93" t="s">
+      <c r="D37" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="100"/>
-      <c r="K37" s="101"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="101"/>
-      <c r="O37" s="102"/>
-      <c r="P37" s="104"/>
-      <c r="Q37" s="105"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="76"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="107"/>
-      <c r="H38" s="107"/>
-      <c r="I38" s="107"/>
-      <c r="J38" s="107"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="101"/>
-      <c r="O38" s="102"/>
-      <c r="P38" s="104"/>
-      <c r="Q38" s="108"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="109" t="s">
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="64"/>
+    </row>
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A38" s="38"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="62"/>
+      <c r="N38" s="60"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="67"/>
+    </row>
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A39" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="110"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="110"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="112" t="s">
+      <c r="B39" s="119"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+      <c r="H39" s="119"/>
+      <c r="I39" s="119"/>
+      <c r="J39" s="119"/>
+      <c r="K39" s="68"/>
+      <c r="L39" s="69"/>
+      <c r="M39" s="68"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="P39" s="113"/>
-      <c r="Q39" s="114" t="str">
+      <c r="P39" s="71"/>
+      <c r="Q39" s="72" t="e">
         <f>Q17-Q30</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="115" t="s">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A40" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="116" t="s">
+      <c r="B40" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="Q40" s="13"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="117"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="11" t="s">
+      <c r="C40" s="116"/>
+      <c r="D40" s="116"/>
+      <c r="E40" s="116"/>
+      <c r="F40" s="116"/>
+      <c r="G40" s="116"/>
+      <c r="H40" s="116"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="116"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="116"/>
+      <c r="M40" s="116"/>
+      <c r="N40" s="116"/>
+      <c r="O40" s="116"/>
+      <c r="P40" s="116"/>
+      <c r="Q40" s="121"/>
+    </row>
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A41" s="74"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="118"/>
-      <c r="M41" s="118"/>
-      <c r="N41" s="30"/>
-      <c r="O41" s="118"/>
-      <c r="P41" s="119"/>
-      <c r="Q41" s="7"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="117"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="118"/>
-      <c r="M42" s="118"/>
-      <c r="N42" s="30"/>
-      <c r="O42" s="118"/>
-      <c r="P42" s="119"/>
-      <c r="Q42" s="7"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="117"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="118"/>
-      <c r="M43" s="118"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="118"/>
-      <c r="P43" s="119"/>
-      <c r="Q43" s="7"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="117"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="118"/>
-      <c r="M44" s="118"/>
-      <c r="N44" s="30"/>
-      <c r="O44" s="118"/>
-      <c r="P44" s="119"/>
-      <c r="Q44" s="7"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="120"/>
-      <c r="Q45" s="13"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="121" t="s">
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="76"/>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A42" s="74"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="75"/>
+      <c r="M42" s="75"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="75"/>
+      <c r="P42" s="76"/>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A43" s="74"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="76"/>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A44" s="74"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="75"/>
+      <c r="M44" s="75"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="75"/>
+      <c r="P44" s="76"/>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A45" s="122"/>
+      <c r="B45" s="116"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="116"/>
+      <c r="F45" s="116"/>
+      <c r="G45" s="116"/>
+      <c r="H45" s="116"/>
+      <c r="I45" s="116"/>
+      <c r="J45" s="116"/>
+      <c r="K45" s="116"/>
+      <c r="L45" s="116"/>
+      <c r="M45" s="116"/>
+      <c r="N45" s="116"/>
+      <c r="O45" s="116"/>
+      <c r="P45" s="116"/>
+      <c r="Q45" s="121"/>
+    </row>
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A46" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="Q46" s="13"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="122" t="s">
+      <c r="B46" s="116"/>
+      <c r="C46" s="116"/>
+      <c r="D46" s="116"/>
+      <c r="E46" s="116"/>
+      <c r="F46" s="116"/>
+      <c r="G46" s="116"/>
+      <c r="H46" s="116"/>
+      <c r="I46" s="116"/>
+      <c r="J46" s="116"/>
+      <c r="K46" s="116"/>
+      <c r="L46" s="116"/>
+      <c r="M46" s="116"/>
+      <c r="N46" s="116"/>
+      <c r="O46" s="116"/>
+      <c r="P46" s="116"/>
+      <c r="Q46" s="121"/>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A47" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B47" s="123" t="s">
+      <c r="B47" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="124"/>
-      <c r="D47" s="124"/>
-      <c r="E47" s="124"/>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="124"/>
-      <c r="L47" s="124"/>
-      <c r="M47" s="124"/>
-      <c r="N47" s="124"/>
-      <c r="O47" s="124"/>
-      <c r="P47" s="124"/>
-      <c r="Q47" s="125"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="126" t="s">
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="79"/>
+      <c r="G47" s="79"/>
+      <c r="H47" s="79"/>
+      <c r="I47" s="79"/>
+      <c r="J47" s="79"/>
+      <c r="K47" s="79"/>
+      <c r="L47" s="79"/>
+      <c r="M47" s="79"/>
+      <c r="N47" s="79"/>
+      <c r="O47" s="79"/>
+      <c r="P47" s="79"/>
+      <c r="Q47" s="80"/>
+    </row>
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A48" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="127"/>
-      <c r="C48" s="127"/>
-      <c r="D48" s="127"/>
-      <c r="E48" s="127"/>
-      <c r="F48" s="127"/>
-      <c r="G48" s="127"/>
-      <c r="H48" s="127"/>
-      <c r="I48" s="127"/>
-      <c r="J48" s="127"/>
-      <c r="K48" s="128" t="s">
+      <c r="B48" s="125"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="125"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="125"/>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="125"/>
+      <c r="J48" s="125"/>
+      <c r="K48" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="L48" s="127"/>
-      <c r="M48" s="129"/>
-      <c r="N48" s="130"/>
-      <c r="O48" s="131"/>
-      <c r="P48" s="132" t="s">
+      <c r="L48" s="125"/>
+      <c r="M48" s="126"/>
+      <c r="N48" s="81"/>
+      <c r="O48" s="82"/>
+      <c r="P48" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="Q48" s="133" t="s">
+      <c r="Q48" s="84" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="134"/>
-      <c r="B49" s="135" t="s">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A49" s="85"/>
+      <c r="B49" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="J49" s="64"/>
-      <c r="K49" s="136" t="s">
+      <c r="C49" s="116"/>
+      <c r="D49" s="116"/>
+      <c r="E49" s="116"/>
+      <c r="F49" s="116"/>
+      <c r="G49" s="116"/>
+      <c r="H49" s="116"/>
+      <c r="I49" s="116"/>
+      <c r="J49" s="129"/>
+      <c r="K49" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="M49" s="64"/>
-      <c r="N49" s="137" t="str">
+      <c r="L49" s="116"/>
+      <c r="M49" s="129"/>
+      <c r="N49" s="131" t="e">
         <f>Q39</f>
         <v>#REF!</v>
       </c>
-      <c r="O49" s="46"/>
-      <c r="P49" s="138"/>
-      <c r="Q49" s="139"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="134"/>
-      <c r="B50" s="135"/>
-      <c r="C50" s="135"/>
-      <c r="D50" s="135"/>
-      <c r="E50" s="135"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="135"/>
-      <c r="H50" s="135"/>
-      <c r="I50" s="135"/>
-      <c r="J50" s="135"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="141"/>
-      <c r="M50" s="142"/>
-      <c r="N50" s="141"/>
-      <c r="O50" s="141"/>
-      <c r="P50" s="143"/>
-      <c r="Q50" s="139"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="144"/>
-      <c r="B51" s="145" t="s">
+      <c r="O49" s="132"/>
+      <c r="P49" s="133"/>
+      <c r="Q49" s="87"/>
+    </row>
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A50" s="85"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="86"/>
+      <c r="H50" s="86"/>
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+      <c r="K50" s="88"/>
+      <c r="L50" s="89"/>
+      <c r="M50" s="90"/>
+      <c r="N50" s="89"/>
+      <c r="O50" s="89"/>
+      <c r="P50" s="91"/>
+      <c r="Q50" s="87"/>
+    </row>
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A51" s="92"/>
+      <c r="B51" s="134" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="146" t="s">
+      <c r="C51" s="119"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="119"/>
+      <c r="H51" s="119"/>
+      <c r="I51" s="119"/>
+      <c r="J51" s="119"/>
+      <c r="K51" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="L51" s="34"/>
-      <c r="M51" s="147"/>
-      <c r="N51" s="148"/>
-      <c r="O51" s="148"/>
-      <c r="P51" s="149"/>
-      <c r="Q51" s="150" t="str">
+      <c r="L51" s="119"/>
+      <c r="M51" s="136"/>
+      <c r="N51" s="93"/>
+      <c r="O51" s="93"/>
+      <c r="P51" s="94"/>
+      <c r="Q51" s="95" t="e">
         <f>N49</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="151" t="s">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A52" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="152" t="s">
+      <c r="B52" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="153" t="s">
+      <c r="C52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="119"/>
+      <c r="K52" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="L52" s="37" t="s">
+      <c r="L52" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="49"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="154"/>
-      <c r="B53" s="155"/>
-      <c r="C53" s="156" t="s">
+      <c r="M52" s="119"/>
+      <c r="N52" s="119"/>
+      <c r="O52" s="119"/>
+      <c r="P52" s="119"/>
+      <c r="Q52" s="139"/>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A53" s="98"/>
+      <c r="B53" s="99"/>
+      <c r="C53" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="156"/>
-      <c r="E53" s="156"/>
-      <c r="F53" s="156"/>
-      <c r="G53" s="156"/>
-      <c r="H53" s="156"/>
-      <c r="I53" s="156"/>
-      <c r="J53" s="156"/>
-      <c r="K53" s="157" t="s">
+      <c r="D53" s="100"/>
+      <c r="E53" s="100"/>
+      <c r="F53" s="100"/>
+      <c r="G53" s="100"/>
+      <c r="H53" s="100"/>
+      <c r="I53" s="100"/>
+      <c r="J53" s="100"/>
+      <c r="K53" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="76"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="158" t="s">
+      <c r="L53" s="141"/>
+      <c r="M53" s="141"/>
+      <c r="N53" s="141"/>
+      <c r="O53" s="141"/>
+      <c r="P53" s="141"/>
+      <c r="Q53" s="142"/>
+    </row>
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A54" s="38"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="D54" s="158"/>
-      <c r="E54" s="158"/>
-      <c r="F54" s="158"/>
-      <c r="G54" s="158"/>
-      <c r="H54" s="158"/>
-      <c r="I54" s="158"/>
-      <c r="J54" s="158"/>
-      <c r="K54" s="27"/>
-      <c r="Q54" s="13"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="117"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="158" t="s">
+      <c r="D54" s="101"/>
+      <c r="E54" s="101"/>
+      <c r="F54" s="101"/>
+      <c r="G54" s="101"/>
+      <c r="H54" s="101"/>
+      <c r="I54" s="101"/>
+      <c r="J54" s="101"/>
+      <c r="K54" s="143"/>
+      <c r="L54" s="116"/>
+      <c r="M54" s="116"/>
+      <c r="N54" s="116"/>
+      <c r="O54" s="116"/>
+      <c r="P54" s="116"/>
+      <c r="Q54" s="121"/>
+    </row>
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A55" s="74"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="158"/>
-      <c r="E55" s="158"/>
-      <c r="F55" s="158"/>
-      <c r="G55" s="158"/>
-      <c r="H55" s="158"/>
-      <c r="I55" s="158"/>
-      <c r="J55" s="158"/>
-      <c r="K55" s="27"/>
-      <c r="Q55" s="13"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="159"/>
-      <c r="B56" s="37"/>
-      <c r="C56" s="160" t="s">
+      <c r="D55" s="101"/>
+      <c r="E55" s="101"/>
+      <c r="F55" s="101"/>
+      <c r="G55" s="101"/>
+      <c r="H55" s="101"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="101"/>
+      <c r="K55" s="143"/>
+      <c r="L55" s="116"/>
+      <c r="M55" s="116"/>
+      <c r="N55" s="116"/>
+      <c r="O55" s="116"/>
+      <c r="P55" s="116"/>
+      <c r="Q55" s="121"/>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A56" s="102"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="D56" s="160"/>
-      <c r="E56" s="160"/>
-      <c r="F56" s="160"/>
-      <c r="G56" s="160"/>
-      <c r="H56" s="160"/>
-      <c r="I56" s="160"/>
-      <c r="J56" s="160"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="34"/>
-      <c r="O56" s="34"/>
-      <c r="P56" s="34"/>
-      <c r="Q56" s="49"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="161" t="s">
+      <c r="D56" s="103"/>
+      <c r="E56" s="103"/>
+      <c r="F56" s="103"/>
+      <c r="G56" s="103"/>
+      <c r="H56" s="103"/>
+      <c r="I56" s="103"/>
+      <c r="J56" s="103"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="119"/>
+      <c r="M56" s="119"/>
+      <c r="N56" s="119"/>
+      <c r="O56" s="119"/>
+      <c r="P56" s="119"/>
+      <c r="Q56" s="139"/>
+    </row>
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A57" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="162"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="161" t="s">
+      <c r="B57" s="141"/>
+      <c r="C57" s="148"/>
+      <c r="D57" s="141"/>
+      <c r="E57" s="141"/>
+      <c r="F57" s="141"/>
+      <c r="G57" s="141"/>
+      <c r="H57" s="141"/>
+      <c r="I57" s="141"/>
+      <c r="J57" s="141"/>
+      <c r="K57" s="145" t="s">
         <v>54</v>
       </c>
-      <c r="L57" s="163"/>
-      <c r="M57" s="164"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="165"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="42"/>
-      <c r="K58" s="165"/>
-      <c r="L58" s="166"/>
-      <c r="M58" s="42"/>
-      <c r="N58" s="42"/>
-      <c r="O58" s="42"/>
-      <c r="P58" s="42"/>
-      <c r="Q58" s="9"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="167" t="s">
+      <c r="L57" s="150"/>
+      <c r="M57" s="152"/>
+      <c r="N57" s="141"/>
+      <c r="O57" s="141"/>
+      <c r="P57" s="141"/>
+      <c r="Q57" s="142"/>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A58" s="146"/>
+      <c r="B58" s="147"/>
+      <c r="C58" s="149"/>
+      <c r="D58" s="147"/>
+      <c r="E58" s="147"/>
+      <c r="F58" s="147"/>
+      <c r="G58" s="147"/>
+      <c r="H58" s="147"/>
+      <c r="I58" s="147"/>
+      <c r="J58" s="147"/>
+      <c r="K58" s="146"/>
+      <c r="L58" s="151"/>
+      <c r="M58" s="147"/>
+      <c r="N58" s="147"/>
+      <c r="O58" s="147"/>
+      <c r="P58" s="147"/>
+      <c r="Q58" s="153"/>
+    </row>
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A59" s="154" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="46"/>
-      <c r="C59" s="168"/>
-      <c r="D59" s="46"/>
-      <c r="E59" s="46"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="46"/>
-      <c r="I59" s="46"/>
-      <c r="J59" s="46"/>
-      <c r="K59" s="169" t="s">
+      <c r="B59" s="132"/>
+      <c r="C59" s="155"/>
+      <c r="D59" s="132"/>
+      <c r="E59" s="132"/>
+      <c r="F59" s="132"/>
+      <c r="G59" s="132"/>
+      <c r="H59" s="132"/>
+      <c r="I59" s="132"/>
+      <c r="J59" s="132"/>
+      <c r="K59" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="L59" s="138"/>
-      <c r="M59" s="170"/>
-      <c r="N59" s="46"/>
-      <c r="O59" s="46"/>
-      <c r="P59" s="46"/>
-      <c r="Q59" s="18"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="165"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="42"/>
-      <c r="K60" s="165"/>
-      <c r="L60" s="166"/>
-      <c r="M60" s="42"/>
-      <c r="N60" s="42"/>
-      <c r="O60" s="42"/>
-      <c r="P60" s="42"/>
-      <c r="Q60" s="9"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="167" t="s">
+      <c r="L59" s="133"/>
+      <c r="M59" s="205"/>
+      <c r="N59" s="132"/>
+      <c r="O59" s="132"/>
+      <c r="P59" s="132"/>
+      <c r="Q59" s="158"/>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A60" s="146"/>
+      <c r="B60" s="147"/>
+      <c r="C60" s="149"/>
+      <c r="D60" s="147"/>
+      <c r="E60" s="147"/>
+      <c r="F60" s="147"/>
+      <c r="G60" s="147"/>
+      <c r="H60" s="147"/>
+      <c r="I60" s="147"/>
+      <c r="J60" s="147"/>
+      <c r="K60" s="146"/>
+      <c r="L60" s="151"/>
+      <c r="M60" s="147"/>
+      <c r="N60" s="147"/>
+      <c r="O60" s="147"/>
+      <c r="P60" s="147"/>
+      <c r="Q60" s="153"/>
+    </row>
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A61" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="46"/>
-      <c r="C61" s="171" t="s">
+      <c r="B61" s="132"/>
+      <c r="C61" s="157" t="s">
         <v>57</v>
       </c>
-      <c r="D61" s="46"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="46"/>
-      <c r="G61" s="46"/>
-      <c r="H61" s="46"/>
-      <c r="I61" s="46"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="169" t="s">
+      <c r="D61" s="132"/>
+      <c r="E61" s="132"/>
+      <c r="F61" s="132"/>
+      <c r="G61" s="132"/>
+      <c r="H61" s="132"/>
+      <c r="I61" s="132"/>
+      <c r="J61" s="158"/>
+      <c r="K61" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="L61" s="138"/>
-      <c r="M61" s="171" t="s">
+      <c r="L61" s="133"/>
+      <c r="M61" s="157" t="s">
         <v>58</v>
       </c>
-      <c r="N61" s="46"/>
-      <c r="O61" s="46"/>
-      <c r="P61" s="46"/>
-      <c r="Q61" s="18"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="27"/>
-      <c r="C62" s="172" t="s">
+      <c r="N61" s="132"/>
+      <c r="O61" s="132"/>
+      <c r="P61" s="132"/>
+      <c r="Q61" s="158"/>
+    </row>
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A62" s="143"/>
+      <c r="B62" s="116"/>
+      <c r="C62" s="159" t="s">
         <v>59</v>
       </c>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="64"/>
-      <c r="M62" s="173" t="s">
+      <c r="D62" s="147"/>
+      <c r="E62" s="147"/>
+      <c r="F62" s="147"/>
+      <c r="G62" s="147"/>
+      <c r="H62" s="147"/>
+      <c r="I62" s="147"/>
+      <c r="J62" s="147"/>
+      <c r="K62" s="143"/>
+      <c r="L62" s="129"/>
+      <c r="M62" s="160" t="s">
         <v>60</v>
       </c>
-      <c r="N62" s="42"/>
-      <c r="O62" s="42"/>
-      <c r="P62" s="42"/>
-      <c r="Q62" s="9"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="55" t="s">
+      <c r="N62" s="147"/>
+      <c r="O62" s="147"/>
+      <c r="P62" s="147"/>
+      <c r="Q62" s="153"/>
+    </row>
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A63" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="46"/>
-      <c r="C63" s="174"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="46"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="46"/>
-      <c r="I63" s="46"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="55" t="s">
+      <c r="B63" s="132"/>
+      <c r="C63" s="173"/>
+      <c r="D63" s="132"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="132"/>
+      <c r="H63" s="132"/>
+      <c r="I63" s="132"/>
+      <c r="J63" s="132"/>
+      <c r="K63" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="L63" s="138"/>
-      <c r="M63" s="175"/>
-      <c r="N63" s="46"/>
-      <c r="O63" s="46"/>
-      <c r="P63" s="46"/>
-      <c r="Q63" s="18"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="33"/>
-      <c r="B64" s="34"/>
-      <c r="C64" s="48"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="34"/>
-      <c r="I64" s="34"/>
-      <c r="J64" s="34"/>
-      <c r="K64" s="33"/>
-      <c r="L64" s="147"/>
-      <c r="M64" s="34"/>
-      <c r="N64" s="34"/>
-      <c r="O64" s="34"/>
-      <c r="P64" s="34"/>
-      <c r="Q64" s="49"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="122" t="s">
+      <c r="L63" s="133"/>
+      <c r="M63" s="174"/>
+      <c r="N63" s="132"/>
+      <c r="O63" s="132"/>
+      <c r="P63" s="132"/>
+      <c r="Q63" s="158"/>
+    </row>
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A64" s="144"/>
+      <c r="B64" s="119"/>
+      <c r="C64" s="166"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="119"/>
+      <c r="H64" s="119"/>
+      <c r="I64" s="119"/>
+      <c r="J64" s="119"/>
+      <c r="K64" s="144"/>
+      <c r="L64" s="136"/>
+      <c r="M64" s="119"/>
+      <c r="N64" s="119"/>
+      <c r="O64" s="119"/>
+      <c r="P64" s="119"/>
+      <c r="Q64" s="139"/>
+    </row>
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A65" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="B65" s="176" t="s">
+      <c r="B65" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="51"/>
-      <c r="K65" s="51"/>
-      <c r="L65" s="51"/>
-      <c r="M65" s="51"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="53"/>
-      <c r="P65" s="177" t="s">
+      <c r="C65" s="176"/>
+      <c r="D65" s="176"/>
+      <c r="E65" s="176"/>
+      <c r="F65" s="176"/>
+      <c r="G65" s="176"/>
+      <c r="H65" s="176"/>
+      <c r="I65" s="176"/>
+      <c r="J65" s="176"/>
+      <c r="K65" s="176"/>
+      <c r="L65" s="176"/>
+      <c r="M65" s="176"/>
+      <c r="N65" s="176"/>
+      <c r="O65" s="177"/>
+      <c r="P65" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="Q65" s="178"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="179" t="s">
+      <c r="Q65" s="105"/>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A66" s="167" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="46"/>
-      <c r="C66" s="60"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="46"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="46"/>
-      <c r="I66" s="138"/>
-      <c r="J66" s="180" t="s">
+      <c r="B66" s="132"/>
+      <c r="C66" s="168"/>
+      <c r="D66" s="132"/>
+      <c r="E66" s="132"/>
+      <c r="F66" s="132"/>
+      <c r="G66" s="132"/>
+      <c r="H66" s="132"/>
+      <c r="I66" s="133"/>
+      <c r="J66" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="K66" s="181" t="s">
+      <c r="K66" s="162" t="s">
         <v>67</v>
       </c>
-      <c r="L66" s="46"/>
-      <c r="M66" s="46"/>
-      <c r="N66" s="46"/>
-      <c r="O66" s="138"/>
-      <c r="P66" s="182" t="s">
+      <c r="L66" s="132"/>
+      <c r="M66" s="132"/>
+      <c r="N66" s="132"/>
+      <c r="O66" s="133"/>
+      <c r="P66" s="165" t="s">
         <v>68</v>
       </c>
-      <c r="Q66" s="13"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="165"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="41"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42"/>
-      <c r="I67" s="166"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="183"/>
-      <c r="L67" s="42"/>
-      <c r="M67" s="42"/>
-      <c r="N67" s="42"/>
-      <c r="O67" s="166"/>
-      <c r="P67" s="41"/>
-      <c r="Q67" s="9"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="179" t="s">
+      <c r="Q66" s="121"/>
+    </row>
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A67" s="146"/>
+      <c r="B67" s="147"/>
+      <c r="C67" s="149"/>
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="147"/>
+      <c r="H67" s="147"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="149"/>
+      <c r="K67" s="163"/>
+      <c r="L67" s="147"/>
+      <c r="M67" s="147"/>
+      <c r="N67" s="147"/>
+      <c r="O67" s="151"/>
+      <c r="P67" s="149"/>
+      <c r="Q67" s="153"/>
+    </row>
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A68" s="167" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="60"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="138"/>
-      <c r="J68" s="180" t="s">
+      <c r="B68" s="132"/>
+      <c r="C68" s="168"/>
+      <c r="D68" s="132"/>
+      <c r="E68" s="132"/>
+      <c r="F68" s="132"/>
+      <c r="G68" s="132"/>
+      <c r="H68" s="132"/>
+      <c r="I68" s="133"/>
+      <c r="J68" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="K68" s="181" t="s">
+      <c r="K68" s="162" t="s">
         <v>70</v>
       </c>
-      <c r="L68" s="46"/>
-      <c r="M68" s="46"/>
-      <c r="N68" s="46"/>
-      <c r="O68" s="138"/>
-      <c r="P68" s="56" t="s">
+      <c r="L68" s="132"/>
+      <c r="M68" s="132"/>
+      <c r="N68" s="132"/>
+      <c r="O68" s="133"/>
+      <c r="P68" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="Q68" s="184"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="165"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="166"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="185"/>
-      <c r="L69" s="42"/>
-      <c r="M69" s="42"/>
-      <c r="N69" s="42"/>
-      <c r="O69" s="166"/>
-      <c r="P69" s="182" t="s">
+      <c r="Q68" s="106"/>
+    </row>
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A69" s="146"/>
+      <c r="B69" s="147"/>
+      <c r="C69" s="149"/>
+      <c r="D69" s="147"/>
+      <c r="E69" s="147"/>
+      <c r="F69" s="147"/>
+      <c r="G69" s="147"/>
+      <c r="H69" s="147"/>
+      <c r="I69" s="151"/>
+      <c r="J69" s="149"/>
+      <c r="K69" s="164"/>
+      <c r="L69" s="147"/>
+      <c r="M69" s="147"/>
+      <c r="N69" s="147"/>
+      <c r="O69" s="151"/>
+      <c r="P69" s="165" t="s">
         <v>68</v>
       </c>
-      <c r="Q69" s="13"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="186" t="s">
+      <c r="Q69" s="121"/>
+    </row>
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A70" s="169" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="187"/>
-      <c r="C70" s="187"/>
-      <c r="D70" s="187"/>
-      <c r="E70" s="187"/>
-      <c r="F70" s="187"/>
-      <c r="G70" s="187"/>
-      <c r="H70" s="187"/>
-      <c r="I70" s="187"/>
-      <c r="J70" s="187"/>
-      <c r="K70" s="187"/>
-      <c r="L70" s="187"/>
-      <c r="M70" s="187"/>
-      <c r="N70" s="187"/>
-      <c r="O70" s="188"/>
-      <c r="P70" s="48"/>
-      <c r="Q70" s="49"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="189"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
-      <c r="P71" s="12"/>
-      <c r="Q71" s="12"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="189"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="11"/>
-      <c r="P72" s="12"/>
-      <c r="Q72" s="12"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="189"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="11"/>
-      <c r="P73" s="12"/>
-      <c r="Q73" s="12"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="189"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="11"/>
-      <c r="P74" s="12"/>
-      <c r="Q74" s="12"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="190"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
-      <c r="J75" s="30"/>
-      <c r="K75" s="30"/>
-      <c r="L75" s="30"/>
-      <c r="M75" s="30"/>
-      <c r="N75" s="30"/>
-      <c r="O75" s="30"/>
-      <c r="P75" s="30"/>
-      <c r="Q75" s="30"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="191"/>
-      <c r="B76" s="192"/>
-      <c r="C76" s="192"/>
-      <c r="D76" s="192"/>
-      <c r="E76" s="192"/>
-      <c r="F76" s="192"/>
-      <c r="G76" s="192"/>
-      <c r="H76" s="192"/>
-      <c r="I76" s="192"/>
-      <c r="J76" s="192"/>
-      <c r="K76" s="192"/>
-      <c r="L76" s="192"/>
-      <c r="M76" s="192"/>
-      <c r="N76" s="192"/>
-      <c r="O76" s="192"/>
-      <c r="P76" s="192"/>
-      <c r="Q76" s="192"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="191"/>
-      <c r="B77" s="192"/>
-      <c r="C77" s="192"/>
-      <c r="D77" s="192"/>
-      <c r="E77" s="192"/>
-      <c r="F77" s="192"/>
-      <c r="G77" s="192"/>
-      <c r="H77" s="192"/>
-      <c r="I77" s="192"/>
-      <c r="J77" s="192"/>
-      <c r="K77" s="192"/>
-      <c r="L77" s="192"/>
-      <c r="M77" s="192"/>
-      <c r="N77" s="192"/>
-      <c r="O77" s="192"/>
-      <c r="P77" s="192"/>
-      <c r="Q77" s="192"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="193"/>
-      <c r="B78" s="192"/>
-      <c r="C78" s="192"/>
-      <c r="D78" s="192"/>
-      <c r="E78" s="192"/>
-      <c r="F78" s="192"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="192"/>
-      <c r="I78" s="192"/>
-      <c r="J78" s="192"/>
-      <c r="K78" s="192"/>
-      <c r="L78" s="192"/>
-      <c r="M78" s="192"/>
-      <c r="N78" s="192"/>
-      <c r="O78" s="192"/>
-      <c r="P78" s="192"/>
-      <c r="Q78" s="192"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="194"/>
-      <c r="B79" s="195"/>
-      <c r="C79" s="192"/>
-      <c r="D79" s="192"/>
-      <c r="E79" s="192"/>
-      <c r="F79" s="192"/>
-      <c r="G79" s="192"/>
-      <c r="H79" s="192"/>
-      <c r="I79" s="192"/>
-      <c r="J79" s="192"/>
-      <c r="K79" s="192"/>
-      <c r="L79" s="192"/>
-      <c r="M79" s="192"/>
-      <c r="N79" s="192"/>
-      <c r="O79" s="192"/>
-      <c r="P79" s="192"/>
-      <c r="Q79" s="192"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="194"/>
-      <c r="B80" s="195"/>
-      <c r="C80" s="192"/>
-      <c r="D80" s="192"/>
-      <c r="E80" s="192"/>
-      <c r="F80" s="192"/>
-      <c r="G80" s="192"/>
-      <c r="H80" s="192"/>
-      <c r="I80" s="192"/>
-      <c r="J80" s="192"/>
-      <c r="K80" s="192"/>
-      <c r="L80" s="192"/>
-      <c r="M80" s="192"/>
-      <c r="N80" s="192"/>
-      <c r="O80" s="192"/>
-      <c r="P80" s="192"/>
-      <c r="Q80" s="192"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="194"/>
-      <c r="B81" s="195"/>
-      <c r="C81" s="192"/>
-      <c r="D81" s="192"/>
-      <c r="E81" s="192"/>
-      <c r="F81" s="192"/>
-      <c r="G81" s="192"/>
-      <c r="H81" s="192"/>
-      <c r="I81" s="192"/>
-      <c r="J81" s="192"/>
-      <c r="K81" s="192"/>
-      <c r="L81" s="192"/>
-      <c r="M81" s="192"/>
-      <c r="N81" s="192"/>
-      <c r="O81" s="192"/>
-      <c r="P81" s="192"/>
-      <c r="Q81" s="192"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="196"/>
-      <c r="B82" s="195"/>
-      <c r="C82" s="192"/>
-      <c r="D82" s="192"/>
-      <c r="E82" s="192"/>
-      <c r="F82" s="192"/>
-      <c r="G82" s="192"/>
-      <c r="H82" s="192"/>
-      <c r="I82" s="192"/>
-      <c r="J82" s="192"/>
-      <c r="K82" s="192"/>
-      <c r="L82" s="192"/>
-      <c r="M82" s="192"/>
-      <c r="N82" s="192"/>
-      <c r="O82" s="192"/>
-      <c r="P82" s="192"/>
-      <c r="Q82" s="192"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="77"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="77"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="77"/>
-      <c r="I83" s="77"/>
-      <c r="J83" s="77"/>
-      <c r="K83" s="77"/>
-      <c r="L83" s="77"/>
-      <c r="M83" s="77"/>
-      <c r="N83" s="77"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="77"/>
-      <c r="Q83" s="77"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="77"/>
-      <c r="B84" s="77"/>
-      <c r="C84" s="77"/>
-      <c r="D84" s="77"/>
-      <c r="E84" s="77"/>
-      <c r="F84" s="77"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="77"/>
-      <c r="I84" s="77"/>
-      <c r="J84" s="77"/>
-      <c r="K84" s="77"/>
-      <c r="L84" s="77"/>
-      <c r="M84" s="77"/>
-      <c r="N84" s="77"/>
-      <c r="O84" s="77"/>
-      <c r="P84" s="77"/>
-      <c r="Q84" s="77"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="77"/>
-      <c r="B85" s="77"/>
-      <c r="C85" s="77"/>
-      <c r="D85" s="77"/>
-      <c r="E85" s="77"/>
-      <c r="F85" s="77"/>
-      <c r="G85" s="77"/>
-      <c r="H85" s="77"/>
-      <c r="I85" s="77"/>
-      <c r="J85" s="77"/>
-      <c r="K85" s="77"/>
-      <c r="L85" s="77"/>
-      <c r="M85" s="77"/>
-      <c r="N85" s="77"/>
-      <c r="O85" s="77"/>
-      <c r="P85" s="77"/>
-      <c r="Q85" s="77"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+      <c r="B70" s="170"/>
+      <c r="C70" s="170"/>
+      <c r="D70" s="170"/>
+      <c r="E70" s="170"/>
+      <c r="F70" s="170"/>
+      <c r="G70" s="170"/>
+      <c r="H70" s="170"/>
+      <c r="I70" s="170"/>
+      <c r="J70" s="170"/>
+      <c r="K70" s="170"/>
+      <c r="L70" s="170"/>
+      <c r="M70" s="170"/>
+      <c r="N70" s="170"/>
+      <c r="O70" s="171"/>
+      <c r="P70" s="166"/>
+      <c r="Q70" s="139"/>
+    </row>
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A71" s="107"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+    </row>
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A72" s="107"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+    </row>
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A73" s="107"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+    </row>
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A74" s="107"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="6"/>
+    </row>
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A75" s="108"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="13"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="13"/>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="13"/>
+      <c r="P75" s="13"/>
+      <c r="Q75" s="13"/>
+    </row>
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A76" s="109"/>
+      <c r="B76" s="110"/>
+      <c r="C76" s="110"/>
+      <c r="D76" s="110"/>
+      <c r="E76" s="110"/>
+      <c r="F76" s="110"/>
+      <c r="G76" s="110"/>
+      <c r="H76" s="110"/>
+      <c r="I76" s="110"/>
+      <c r="J76" s="110"/>
+      <c r="K76" s="110"/>
+      <c r="L76" s="110"/>
+      <c r="M76" s="110"/>
+      <c r="N76" s="110"/>
+      <c r="O76" s="110"/>
+      <c r="P76" s="110"/>
+      <c r="Q76" s="110"/>
+    </row>
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A77" s="109"/>
+      <c r="B77" s="110"/>
+      <c r="C77" s="110"/>
+      <c r="D77" s="110"/>
+      <c r="E77" s="110"/>
+      <c r="F77" s="110"/>
+      <c r="G77" s="110"/>
+      <c r="H77" s="110"/>
+      <c r="I77" s="110"/>
+      <c r="J77" s="110"/>
+      <c r="K77" s="110"/>
+      <c r="L77" s="110"/>
+      <c r="M77" s="110"/>
+      <c r="N77" s="110"/>
+      <c r="O77" s="110"/>
+      <c r="P77" s="110"/>
+      <c r="Q77" s="110"/>
+    </row>
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A78" s="111"/>
+      <c r="B78" s="110"/>
+      <c r="C78" s="110"/>
+      <c r="D78" s="110"/>
+      <c r="E78" s="110"/>
+      <c r="F78" s="110"/>
+      <c r="G78" s="110"/>
+      <c r="H78" s="110"/>
+      <c r="I78" s="110"/>
+      <c r="J78" s="110"/>
+      <c r="K78" s="110"/>
+      <c r="L78" s="110"/>
+      <c r="M78" s="110"/>
+      <c r="N78" s="110"/>
+      <c r="O78" s="110"/>
+      <c r="P78" s="110"/>
+      <c r="Q78" s="110"/>
+    </row>
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A79" s="112"/>
+      <c r="B79" s="113"/>
+      <c r="C79" s="110"/>
+      <c r="D79" s="110"/>
+      <c r="E79" s="110"/>
+      <c r="F79" s="110"/>
+      <c r="G79" s="110"/>
+      <c r="H79" s="110"/>
+      <c r="I79" s="110"/>
+      <c r="J79" s="110"/>
+      <c r="K79" s="110"/>
+      <c r="L79" s="110"/>
+      <c r="M79" s="110"/>
+      <c r="N79" s="110"/>
+      <c r="O79" s="110"/>
+      <c r="P79" s="110"/>
+      <c r="Q79" s="110"/>
+    </row>
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A80" s="112"/>
+      <c r="B80" s="113"/>
+      <c r="C80" s="110"/>
+      <c r="D80" s="110"/>
+      <c r="E80" s="110"/>
+      <c r="F80" s="110"/>
+      <c r="G80" s="110"/>
+      <c r="H80" s="110"/>
+      <c r="I80" s="110"/>
+      <c r="J80" s="110"/>
+      <c r="K80" s="110"/>
+      <c r="L80" s="110"/>
+      <c r="M80" s="110"/>
+      <c r="N80" s="110"/>
+      <c r="O80" s="110"/>
+      <c r="P80" s="110"/>
+      <c r="Q80" s="110"/>
+    </row>
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A81" s="112"/>
+      <c r="B81" s="113"/>
+      <c r="C81" s="110"/>
+      <c r="D81" s="110"/>
+      <c r="E81" s="110"/>
+      <c r="F81" s="110"/>
+      <c r="G81" s="110"/>
+      <c r="H81" s="110"/>
+      <c r="I81" s="110"/>
+      <c r="J81" s="110"/>
+      <c r="K81" s="110"/>
+      <c r="L81" s="110"/>
+      <c r="M81" s="110"/>
+      <c r="N81" s="110"/>
+      <c r="O81" s="110"/>
+      <c r="P81" s="110"/>
+      <c r="Q81" s="110"/>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A82" s="114"/>
+      <c r="B82" s="113"/>
+      <c r="C82" s="110"/>
+      <c r="D82" s="110"/>
+      <c r="E82" s="110"/>
+      <c r="F82" s="110"/>
+      <c r="G82" s="110"/>
+      <c r="H82" s="110"/>
+      <c r="I82" s="110"/>
+      <c r="J82" s="110"/>
+      <c r="K82" s="110"/>
+      <c r="L82" s="110"/>
+      <c r="M82" s="110"/>
+      <c r="N82" s="110"/>
+      <c r="O82" s="110"/>
+      <c r="P82" s="110"/>
+      <c r="Q82" s="110"/>
+    </row>
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A83" s="39"/>
+      <c r="B83" s="39"/>
+      <c r="C83" s="39"/>
+      <c r="D83" s="39"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="39"/>
+      <c r="H83" s="39"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="39"/>
+      <c r="K83" s="39"/>
+      <c r="L83" s="39"/>
+      <c r="M83" s="39"/>
+      <c r="N83" s="39"/>
+      <c r="O83" s="39"/>
+      <c r="P83" s="39"/>
+      <c r="Q83" s="39"/>
+    </row>
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
+      <c r="J84" s="39"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="39"/>
+      <c r="N84" s="39"/>
+      <c r="O84" s="39"/>
+      <c r="P84" s="39"/>
+      <c r="Q84" s="39"/>
+    </row>
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A85" s="39"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="39"/>
+      <c r="K85" s="39"/>
+      <c r="L85" s="39"/>
+      <c r="M85" s="39"/>
+      <c r="N85" s="39"/>
+      <c r="O85" s="39"/>
+      <c r="P85" s="39"/>
+      <c r="Q85" s="39"/>
+    </row>
+    <row r="86" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="87" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="88" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="89" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="90" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="91" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="92" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="93" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="95" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="96" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -5153,57 +5519,20 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="81">
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="B40:Q40"/>
-    <mergeCell ref="A45:Q45"/>
-    <mergeCell ref="A46:Q46"/>
-    <mergeCell ref="K48:M48"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="B49:J49"/>
-    <mergeCell ref="K49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="K51:M51"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="L52:Q52"/>
-    <mergeCell ref="K53:Q56"/>
-    <mergeCell ref="A57:B58"/>
-    <mergeCell ref="C57:J58"/>
-    <mergeCell ref="K57:L58"/>
-    <mergeCell ref="M57:Q58"/>
-    <mergeCell ref="A59:B60"/>
-    <mergeCell ref="C59:J60"/>
-    <mergeCell ref="K59:L60"/>
-    <mergeCell ref="A61:B62"/>
-    <mergeCell ref="C61:J61"/>
-    <mergeCell ref="K61:L62"/>
-    <mergeCell ref="C62:J62"/>
-    <mergeCell ref="M62:Q62"/>
-    <mergeCell ref="J66:J67"/>
-    <mergeCell ref="K66:O66"/>
-    <mergeCell ref="K67:O67"/>
-    <mergeCell ref="K68:O68"/>
-    <mergeCell ref="K69:O69"/>
-    <mergeCell ref="P69:Q70"/>
-    <mergeCell ref="A66:B67"/>
-    <mergeCell ref="A68:B69"/>
-    <mergeCell ref="C68:I69"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="A70:O70"/>
-    <mergeCell ref="A63:B64"/>
-    <mergeCell ref="C63:J64"/>
-    <mergeCell ref="K63:L64"/>
-    <mergeCell ref="M63:Q64"/>
-    <mergeCell ref="B65:O65"/>
-    <mergeCell ref="C66:I67"/>
-    <mergeCell ref="P66:Q67"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="D3:O3"/>
-    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="M59:Q60"/>
+    <mergeCell ref="M61:Q61"/>
+    <mergeCell ref="B17:J20"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="C13:Q14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="A15:J15"/>
     <mergeCell ref="D4:O4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="A8:B10"/>
@@ -5220,24 +5549,60 @@
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="C11:J12"/>
     <mergeCell ref="K12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="C13:Q14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="B17:J20"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="M59:Q60"/>
-    <mergeCell ref="M61:Q61"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="A63:B64"/>
+    <mergeCell ref="C63:J64"/>
+    <mergeCell ref="K63:L64"/>
+    <mergeCell ref="M63:Q64"/>
+    <mergeCell ref="B65:O65"/>
+    <mergeCell ref="P69:Q70"/>
+    <mergeCell ref="A66:B67"/>
+    <mergeCell ref="A68:B69"/>
+    <mergeCell ref="C68:I69"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="A70:O70"/>
+    <mergeCell ref="C66:I67"/>
+    <mergeCell ref="P66:Q67"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="K66:O66"/>
+    <mergeCell ref="K67:O67"/>
+    <mergeCell ref="K68:O68"/>
+    <mergeCell ref="K69:O69"/>
+    <mergeCell ref="A61:B62"/>
+    <mergeCell ref="C61:J61"/>
+    <mergeCell ref="K61:L62"/>
+    <mergeCell ref="C62:J62"/>
+    <mergeCell ref="M62:Q62"/>
+    <mergeCell ref="A57:B58"/>
+    <mergeCell ref="C57:J58"/>
+    <mergeCell ref="K57:L58"/>
+    <mergeCell ref="M57:Q58"/>
+    <mergeCell ref="A59:B60"/>
+    <mergeCell ref="C59:J60"/>
+    <mergeCell ref="K59:L60"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="L52:Q52"/>
+    <mergeCell ref="K53:Q56"/>
+    <mergeCell ref="A46:Q46"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="B49:J49"/>
+    <mergeCell ref="K49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="B40:Q40"/>
+    <mergeCell ref="A45:Q45"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.2" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="54" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>